--- a/etf_holdings/2026-10-15_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-15_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5423000</v>
+        <v>8700000</v>
       </c>
       <c r="K2" t="n">
-        <v>5808000</v>
+        <v>9600000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>385,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-14_00981A_full_holdings.xlsx</t>
+          <t>2026-10-14_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,55 +564,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.85%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18721000</v>
+        <v>130000</v>
       </c>
       <c r="K3" t="n">
-        <v>18938000</v>
+        <v>150000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>217,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-14_00981A_full_holdings.xlsx</t>
+          <t>2026-10-14_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,48 +627,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+3.06%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6847000</v>
+        <v>290000</v>
       </c>
       <c r="K4" t="n">
-        <v>7046000</v>
+        <v>320000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>199,000</t>
+          <t>30,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-14_00981A_full_holdings.xlsx</t>
+          <t>2026-10-14_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -690,43 +690,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+2.37%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8700000</v>
+        <v>10000000</v>
       </c>
       <c r="K5" t="n">
-        <v>9600000</v>
+        <v>15000000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -748,48 +748,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.41%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>130000</v>
+        <v>1150020</v>
       </c>
       <c r="K6" t="n">
-        <v>150000</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>-1,149,020</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -801,7 +797,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -811,60 +807,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+3.06%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>290000</v>
+        <v>179000</v>
       </c>
       <c r="K7" t="n">
-        <v>320000</v>
+        <v>129000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>30,000</t>
+          <t>-50,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-14_00991A_full_holdings.xlsx</t>
+          <t>2026-10-14_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -874,60 +870,60 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+2.37%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10000000</v>
+        <v>1672000</v>
       </c>
       <c r="K8" t="n">
-        <v>15000000</v>
+        <v>1022000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>-650,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-14_00991A_full_holdings.xlsx</t>
+          <t>2026-10-14_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,51 +938,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>6.26%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>5.40%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.86%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>1150020</v>
+        <v>1950000</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>1700000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1,149,020</t>
+          <t>-250,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-14_00991A_full_holdings.xlsx</t>
+          <t>2026-10-14_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -996,186 +996,150 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>179000</v>
+        <v>2180000</v>
       </c>
       <c r="K10" t="n">
-        <v>129000</v>
+        <v>2300000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>120,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-14_00982A_full_holdings.xlsx</t>
+          <t>2026-10-14_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>微星</t>
-        </is>
-      </c>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>微星</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.53%</t>
-        </is>
-      </c>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.21%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1672000</v>
-      </c>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>1022000</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-650,000</t>
-        </is>
-      </c>
+        <v>12326000</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-14_00982A_full_holdings.xlsx</t>
+          <t>2026-10-14_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.26%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5.40%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.86%</t>
-        </is>
-      </c>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>1950000</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-250,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-14_00403A_full_holdings.xlsx</t>
+          <t>2026-10-14_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1190,48 +1154,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.53%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2180000</v>
+        <v>11318000</v>
       </c>
       <c r="K13" t="n">
-        <v>2300000</v>
+        <v>16959000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>120,000</t>
+          <t>5,641,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-14_00403A_full_holdings.xlsx</t>
+          <t>2026-10-14_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1243,37 +1207,55 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>遠東新</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.42%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>3.53%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10393000</v>
+      </c>
       <c r="K14" t="n">
-        <v>12326000</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>11645000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1,252,000</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>2026-10-14_00985A_full_holdings.xlsx</t>
@@ -1288,37 +1270,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.99%</t>
+        </is>
+      </c>
       <c r="J15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+        <v>4101000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1158000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-2,943,000</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>2026-10-14_00985A_full_holdings.xlsx</t>
@@ -1343,43 +1343,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+1.00%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>11318000</v>
+        <v>7283000</v>
       </c>
       <c r="K16" t="n">
-        <v>16959000</v>
+        <v>13839000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5,641,000</t>
+          <t>6,556,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,43 +1406,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10393000</v>
+        <v>6940000</v>
       </c>
       <c r="K17" t="n">
-        <v>11645000</v>
+        <v>8299000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1,252,000</t>
+          <t>1,359,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1464,48 +1464,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4101000</v>
+        <v>1223000</v>
       </c>
       <c r="K18" t="n">
-        <v>1158000</v>
+        <v>1579000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-2,943,000</t>
+          <t>356,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1527,48 +1527,48 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7283000</v>
+        <v>693000</v>
       </c>
       <c r="K19" t="n">
-        <v>13839000</v>
+        <v>500000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6,556,000</t>
+          <t>-193,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,43 +1595,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>14.81%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>13.81%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6940000</v>
+        <v>1416000</v>
       </c>
       <c r="K20" t="n">
-        <v>8299000</v>
+        <v>1430000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1,359,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1653,48 +1653,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1223000</v>
+        <v>1498000</v>
       </c>
       <c r="K21" t="n">
-        <v>1579000</v>
+        <v>156000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>356,000</t>
+          <t>-1,342,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1716,48 +1716,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>693000</v>
+        <v>152000</v>
       </c>
       <c r="K22" t="n">
-        <v>500000</v>
+        <v>161000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-193,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,43 +1784,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14.81%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>13.81%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1416000</v>
+        <v>690000</v>
       </c>
       <c r="K23" t="n">
-        <v>1430000</v>
+        <v>894000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>204,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1842,48 +1842,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1498000</v>
+        <v>80000</v>
       </c>
       <c r="K24" t="n">
-        <v>156000</v>
+        <v>102000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-1,342,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1905,48 +1905,48 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>152000</v>
+        <v>16000</v>
       </c>
       <c r="K25" t="n">
-        <v>161000</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>-15,000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,43 +1973,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>690000</v>
+        <v>307000</v>
       </c>
       <c r="K26" t="n">
-        <v>894000</v>
+        <v>380000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>204,000</t>
+          <t>73,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,43 +2036,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="K27" t="n">
-        <v>102000</v>
+        <v>185000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2094,48 +2094,48 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>16000</v>
+        <v>119000</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>134000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-15,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,27 +2162,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2191,14 +2191,14 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>307000</v>
+        <v>243000</v>
       </c>
       <c r="K29" t="n">
-        <v>380000</v>
+        <v>343000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>73,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2220,48 +2220,48 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>160000</v>
+        <v>20000</v>
       </c>
       <c r="K30" t="n">
-        <v>185000</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>-19,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2288,55 +2288,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>119000</v>
+        <v>910013</v>
       </c>
       <c r="K31" t="n">
-        <v>134000</v>
+        <v>1334013</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>424,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-10-14_00985A_full_holdings.xlsx</t>
+          <t>2026-10-14_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2346,60 +2346,60 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>ADVANTEST CORP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>ADVANTEST CORP</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>243000</v>
+        <v>103200</v>
       </c>
       <c r="K32" t="n">
-        <v>343000</v>
+        <v>59400</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>-43,800</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-10-14_00985A_full_holdings.xlsx</t>
+          <t>2026-10-14_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2414,55 +2414,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>LASERTEC CORP</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>LASERTEC CORP</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>20000</v>
+        <v>62100</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>42900</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-19,000</t>
+          <t>-19,200</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-10-14_00985A_full_holdings.xlsx</t>
+          <t>2026-10-14_00990A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2477,55 +2477,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>910013</v>
+        <v>236000</v>
       </c>
       <c r="K34" t="n">
-        <v>1334013</v>
+        <v>306000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>424,000</t>
+          <t>70,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-10-14_00992A_full_holdings.xlsx</t>
+          <t>2026-10-14_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2535,60 +2535,60 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ADVANTEST CORP</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADVANTEST CORP</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>103200</v>
+        <v>483000</v>
       </c>
       <c r="K35" t="n">
-        <v>59400</v>
+        <v>528000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-43,800</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-10-14_00990A_full_holdings.xlsx</t>
+          <t>2026-10-14_00407A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,240 +2598,51 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LASERTEC CORP</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LASERTEC CORP</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>62100</v>
+        <v>804000</v>
       </c>
       <c r="K36" t="n">
-        <v>42900</v>
+        <v>1830000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-19,200</t>
+          <t>1,026,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-10-14_00990A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1.74%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>+0.41%</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>236000</v>
-      </c>
-      <c r="K37" t="n">
-        <v>306000</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>70,000</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-10-14_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>3.09%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>3.39%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>+0.30%</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>483000</v>
-      </c>
-      <c r="K38" t="n">
-        <v>528000</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>45,000</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-10-14_00407A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>台表科</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0.76%</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>1.89%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>+1.13%</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>804000</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1830000</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>1,026,000</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
         <is>
           <t>2026-10-14_00400A_full_holdings.xlsx</t>
         </is>
